--- a/template_nhap_gia GIA RAI.xlsx
+++ b/template_nhap_gia GIA RAI.xlsx
@@ -44,7 +44,7 @@
     <t>Đông Hải</t>
   </si>
   <si>
-    <t>Sóc Trăng cũ, TP Cần Thơ</t>
+    <t>Sóc Trăng, TP Cần Thơ</t>
   </si>
   <si>
     <t>P. Giá Rai, P. Láng Tròn, X. Phong Thạnh</t>
@@ -1244,7 +1244,7 @@
     <col min="3" max="3" width="17.2890625" style="3" customWidth="1"/>
     <col min="4" max="4" width="16" style="4" customWidth="1"/>
     <col min="5" max="5" width="16.2890625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="15.4296875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23.875" style="6" customWidth="1"/>
     <col min="8" max="8" width="15.7890625" customWidth="1"/>
     <col min="9" max="9" width="25.6875" customWidth="1"/>
   </cols>
